--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ÃÂÃÂÃÂÃÂgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ÃÂÃÂgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ÃÂgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -523,7 +523,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ÃÂgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ÃÂgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -563,7 +563,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ÃÂgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -583,7 +583,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ÃÂgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ãgua Clara</t>
+          <t>Água Clara</t>
         </is>
       </c>
       <c r="D9" t="n">

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +630,326 @@
         <v>109</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,6 +950,226 @@
         <v>111</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>111.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>111.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Test 3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -2,22 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preços" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +25,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B4332"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -55,14 +65,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,8 +438,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="7.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="11.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="18.44140625" bestFit="1" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -449,6 +468,11 @@
           <t>Preço Venda (R$/sc)</t>
         </is>
       </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Cultura</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1168,6 +1192,123 @@
       </c>
       <c r="D37" t="n">
         <v>110</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>111</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>110</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>110</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Raphael</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>55</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Milho</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Linneu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Rio Brilhante</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>105</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1213,7 +1213,6 @@
       <c r="D38" t="n">
         <v>111</v>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1234,7 +1233,6 @@
       <c r="D39" t="n">
         <v>110</v>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1306,6 +1304,31 @@
         <v>105</v>
       </c>
       <c r="E42" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Teste</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Aral Moreira</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>111</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>Soja</t>
         </is>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -453,9 +453,9 @@
           <t>Data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Técnico</t>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Informante</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1329,6 +1329,31 @@
         <v>111</v>
       </c>
       <c r="E43" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>José</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Coronel Sapucaia</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>103</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>Soja</t>
         </is>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1359,6 +1359,81 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Produtor - Zé</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>110</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Produtor - Zé</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>111</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Proprietário - Linneu</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Rio Brilhante</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1434,6 +1434,131 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Produtor - Zé</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Anaurilândia</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Milho</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>110</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>111</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>115</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>112</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,16 +31,27 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B4332"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -65,12 +76,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -438,13 +452,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="7.88671875" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="11.88671875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="19" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.77734375" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="18.44140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="7.21875" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +488,21 @@
           <t>Cultura</t>
         </is>
       </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Data de Negociação</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1556,6 +1586,186 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>Soja</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>118</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Produtor - Raphael Gimenes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>110</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gerente - Raphael Gimenes</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>110</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Anastácio</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>110</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>120</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>-20.462172</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-54.581705</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>120</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>-20.462214</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-54.581724</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1613,9 +1613,6 @@
           <t>Soja</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1641,9 +1638,6 @@
           <t>Soja</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1669,9 +1663,6 @@
           <t>Soja</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1697,9 +1688,6 @@
           <t>Soja</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1731,7 +1719,6 @@
       <c r="G57" t="n">
         <v>-54.581705</v>
       </c>
-      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1766,6 +1753,360 @@
       <c r="H58" t="inlineStr">
         <is>
           <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>110</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>-20.462173</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-54.581695</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>111</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>-20.462173</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-54.581695</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>-20.462173</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-54.581695</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Anastácio</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>-20.462173</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-54.581695</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Anastácio</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>-20.462173</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-54.581695</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Anastácio</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>112</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>-20.462173</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-54.581695</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Proprietário - Linneu</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Rio Brilhante</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>140</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>-20.462414</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-54.581836</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Proprietário - Eddu</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Maracaju</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>150</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>-20.462173</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-54.581686</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Produtor</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Água Clara</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>110</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>-20.462165</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-54.581703</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Produtor - Staël Caroline Rego</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Glória de Dourados</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>41</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>

--- a/Dados_Precos.xlsx
+++ b/Dados_Precos.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2110,6 +2110,186 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Gerente - RAPHAEL FLORES GIMENES</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Angélica</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>105</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>-20.46216</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-54.581697</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gerente - RAPHAEL FLORES GIMENES</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Angélica</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>105</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>-20.46216</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-54.581697</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Gerente - RAPHAEL FLORES GIMENES</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Angélica</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>105</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>-20.46216</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-54.581697</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Gerente - Koao</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Angélica</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>106</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>-20.46216</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-54.581697</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Técnico Aprosoja - Mestre jedi</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Campo Grande</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>75</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Milho</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>-20.462348</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-54.581802</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
